--- a/Test cases/API-Test-Cases.xlsx
+++ b/Test cases/API-Test-Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dying\1QA PROJECTS\2- restful-booker-api-testing\Test cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20A5BA3C-04AD-40C4-8C55-AF9C82647B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1A9D12-79A9-4883-94BD-55553D7442A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="99">
   <si>
     <t>ID</t>
   </si>
@@ -211,9 +211,6 @@
     <t>Create booking with missing fields</t>
   </si>
   <si>
-    <t>no booking created</t>
-  </si>
-  <si>
     <t>Verify existance of created booking</t>
   </si>
   <si>
@@ -271,13 +268,61 @@
     <t>no booking found</t>
   </si>
   <si>
-    <t>Verify api status</t>
-  </si>
-  <si>
-    <t>Api running</t>
-  </si>
-  <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>Verify API health endpoint</t>
+  </si>
+  <si>
+    <t>API returns successful health-check response</t>
+  </si>
+  <si>
+    <t>API returns the appropriate error response for a non-existent booking ID.</t>
+  </si>
+  <si>
+    <t>API rejects the request and returns an appropriate validation/error response.</t>
+  </si>
+  <si>
+    <t>API rejects the update request when authentication is missing.</t>
+  </si>
+  <si>
+    <t>Endpoint</t>
+  </si>
+  <si>
+    <t>auth</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>booking</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>booking/:id</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>PATCH</t>
+  </si>
+  <si>
+    <t>ping</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
 </sst>
 </file>
@@ -307,7 +352,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -317,6 +362,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -333,10 +390,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,16 +678,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C926A8-4A04-4306-8E54-7F39C8C098CA}">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="42.33203125" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.109375" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -634,246 +697,442 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="F2" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="F3" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="F4" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="F5" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="F6" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="F7" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="C8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="F9" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="F15" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="F16" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="F17" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="B22" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>82</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -888,7 +1147,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
